--- a/data/trans_orig/POLIPATOLOGIA_5-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2007</t>
+          <t>Población con cinco o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38124</t>
+          <t>36692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57001</t>
+          <t>58582</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667281</t>
+          <t>667063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>683520</t>
+          <t>683029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>650227</t>
+          <t>651659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670727</t>
+          <t>670718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1325362</t>
+          <t>1323781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1350528</t>
+          <t>1350979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48933</t>
+          <t>48915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43044</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73333</t>
+          <t>73661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76078</t>
+          <t>75930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114686</t>
+          <t>113362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>912867</t>
+          <t>912885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>936429</t>
+          <t>936605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>895060</t>
+          <t>894732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>925349</t>
+          <t>925967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1815507</t>
+          <t>1816831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1854115</t>
+          <t>1854263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34562</t>
+          <t>36601</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55739</t>
+          <t>55895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87312</t>
+          <t>85542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76769</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111310</t>
+          <t>113882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643947</t>
+          <t>641908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663169</t>
+          <t>663527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>596529</t>
+          <t>598299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>628102</t>
+          <t>627946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251040</t>
+          <t>1248468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1285581</t>
+          <t>1285423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>24716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48497</t>
+          <t>45853</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60013</t>
+          <t>58436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93354</t>
+          <t>91814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90836</t>
+          <t>91772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130639</t>
+          <t>129530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>893725</t>
+          <t>896369</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916578</t>
+          <t>917506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945258</t>
+          <t>946798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>978599</t>
+          <t>980176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1850195</t>
+          <t>1851304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1889998</t>
+          <t>1889062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92695</t>
+          <t>94626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134837</t>
+          <t>136121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198422</t>
+          <t>199560</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>260679</t>
+          <t>258014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>306644</t>
+          <t>303891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>378429</t>
+          <t>374096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3141706</t>
+          <t>3140422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3183848</t>
+          <t>3181917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3118518</t>
+          <t>3121183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3180775</t>
+          <t>3179637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6277312</t>
+          <t>6281645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6349097</t>
+          <t>6351850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39792</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51709</t>
+          <t>51632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84621</t>
+          <t>85982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76654</t>
+          <t>77501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116246</t>
+          <t>114848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>663677</t>
+          <t>665154</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685109</t>
+          <t>685211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>612429</t>
+          <t>611068</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>645341</t>
+          <t>645418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1284273</t>
+          <t>1285671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1323865</t>
+          <t>1323018</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51130</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76122</t>
+          <t>76542</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113798</t>
+          <t>114765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109395</t>
+          <t>109465</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153666</t>
+          <t>155108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>966817</t>
+          <t>966564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>991986</t>
+          <t>991837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>918386</t>
+          <t>917419</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>956062</t>
+          <t>955642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1896465</t>
+          <t>1895023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1940736</t>
+          <t>1940666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>43022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56481</t>
+          <t>56906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89121</t>
+          <t>89810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83217</t>
+          <t>83503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125588</t>
+          <t>126730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>716002</t>
+          <t>714601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>738097</t>
+          <t>738652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>688053</t>
+          <t>687364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>720693</t>
+          <t>720268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1409209</t>
+          <t>1408067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1451580</t>
+          <t>1451294</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50832</t>
+          <t>51777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97292</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139707</t>
+          <t>140464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132369</t>
+          <t>132547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181672</t>
+          <t>181960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896907</t>
+          <t>895962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922348</t>
+          <t>922522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>912194</t>
+          <t>911437</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>954609</t>
+          <t>954860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1817968</t>
+          <t>1817680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1867271</t>
+          <t>1867093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107465</t>
+          <t>106968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153734</t>
+          <t>156398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>313531</t>
+          <t>316576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>388151</t>
+          <t>388206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>436314</t>
+          <t>438667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>523549</t>
+          <t>522074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3273045</t>
+          <t>3270381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3319314</t>
+          <t>3319811</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3170158</t>
+          <t>3170103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3244778</t>
+          <t>3241733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6461539</t>
+          <t>6463014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6548774</t>
+          <t>6546421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39916</t>
+          <t>40670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59784</t>
+          <t>58928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92422</t>
+          <t>91318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84986</t>
+          <t>85235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123056</t>
+          <t>124531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>634884</t>
+          <t>634130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>656360</t>
+          <t>655604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>580417</t>
+          <t>581521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>613055</t>
+          <t>613911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1224583</t>
+          <t>1223108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1262653</t>
+          <t>1262404</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>21685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45631</t>
+          <t>43225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74068</t>
+          <t>74995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115401</t>
+          <t>115818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102229</t>
+          <t>102365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147503</t>
+          <t>149835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>976800</t>
+          <t>979206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>999615</t>
+          <t>1000746</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>927512</t>
+          <t>927095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>968845</t>
+          <t>967918</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1917841</t>
+          <t>1915509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1963115</t>
+          <t>1962979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>36431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50998</t>
+          <t>51914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84146</t>
+          <t>83534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73444</t>
+          <t>73284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111891</t>
+          <t>112933</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>723079</t>
+          <t>723121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>743351</t>
+          <t>742208</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>700865</t>
+          <t>701477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>734013</t>
+          <t>733097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1432672</t>
+          <t>1431630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1471119</t>
+          <t>1471279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>24294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45652</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93132</t>
+          <t>93884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136237</t>
+          <t>138405</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123545</t>
+          <t>124403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176733</t>
+          <t>175382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891915</t>
+          <t>888955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>915261</t>
+          <t>913273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>907542</t>
+          <t>905374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950647</t>
+          <t>949895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1804613</t>
+          <t>1805964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1857801</t>
+          <t>1856943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97702</t>
+          <t>99319</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142580</t>
+          <t>143874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>310099</t>
+          <t>312428</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>386289</t>
+          <t>390815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>420266</t>
+          <t>422978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>508712</t>
+          <t>509744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3251770</t>
+          <t>3250476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3296648</t>
+          <t>3295031</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3158253</t>
+          <t>3153727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3234443</t>
+          <t>3232114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6430180</t>
+          <t>6429148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6518626</t>
+          <t>6515914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>52785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79864</t>
+          <t>80637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95823</t>
+          <t>98488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>139748</t>
+          <t>140201</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>162001</t>
+          <t>165495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210160</t>
+          <t>210951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>555577</t>
+          <t>554804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>582641</t>
+          <t>582656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>585582</t>
+          <t>585129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>629507</t>
+          <t>626842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1150612</t>
+          <t>1149821</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1198771</t>
+          <t>1195277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43761</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106241</t>
+          <t>105847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134809</t>
+          <t>135388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168779</t>
+          <t>169226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150883</t>
+          <t>154073</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>267638</t>
+          <t>267467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1086623</t>
+          <t>1087017</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1149103</t>
+          <t>1155517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>789872</t>
+          <t>789425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>823842</t>
+          <t>823263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1883878</t>
+          <t>1884049</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2000633</t>
+          <t>1997443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39780</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>67381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125265</t>
+          <t>125105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>581982</t>
+          <t>611821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170692</t>
+          <t>169896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>786807</t>
+          <t>767159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638167</t>
+          <t>637299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664900</t>
+          <t>663940</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>351384</t>
+          <t>321545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>808101</t>
+          <t>808261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>851239</t>
+          <t>870887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1467354</t>
+          <t>1468150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>64008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95053</t>
+          <t>94888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149239</t>
+          <t>151024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210458</t>
+          <t>214421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234068</t>
+          <t>225749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>297009</t>
+          <t>292210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831778</t>
+          <t>831943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>863180</t>
+          <t>862823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>884474</t>
+          <t>880511</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>945693</t>
+          <t>943908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1724754</t>
+          <t>1729553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1787695</t>
+          <t>1796014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>215175</t>
+          <t>214747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>309745</t>
+          <t>311928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>585192</t>
+          <t>584704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1319657</t>
+          <t>1318188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>832624</t>
+          <t>840275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1690428</t>
+          <t>1625930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3150072</t>
+          <t>3147889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3244642</t>
+          <t>3245070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2392623</t>
+          <t>2394092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3127088</t>
+          <t>3127576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5481669</t>
+          <t>5546167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6339473</t>
+          <t>6331822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_5-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>26614</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>17160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36692</t>
+          <t>36817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31384</t>
+          <t>32165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58582</t>
+          <t>57736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667063</t>
+          <t>667398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>683029</t>
+          <t>683521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>651659</t>
+          <t>651534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670718</t>
+          <t>671191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1323781</t>
+          <t>1324627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1350979</t>
+          <t>1350198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>24524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48915</t>
+          <t>48657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42426</t>
+          <t>44340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73661</t>
+          <t>73463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75930</t>
+          <t>74426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113362</t>
+          <t>112331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>912885</t>
+          <t>913143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>936605</t>
+          <t>937276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>894732</t>
+          <t>894930</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>925967</t>
+          <t>924053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1816831</t>
+          <t>1817862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1854263</t>
+          <t>1855767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>15698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36601</t>
+          <t>35479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55895</t>
+          <t>54872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85542</t>
+          <t>86882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76927</t>
+          <t>74710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113882</t>
+          <t>113605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641908</t>
+          <t>643030</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663527</t>
+          <t>662811</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>598299</t>
+          <t>596959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>627946</t>
+          <t>628969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1248468</t>
+          <t>1248745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1285423</t>
+          <t>1287640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>26630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45853</t>
+          <t>47833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58436</t>
+          <t>58295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91814</t>
+          <t>91938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91772</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129530</t>
+          <t>130460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896369</t>
+          <t>894389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917506</t>
+          <t>915592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>946798</t>
+          <t>946674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>980176</t>
+          <t>980317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1851304</t>
+          <t>1850374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1889062</t>
+          <t>1890834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94626</t>
+          <t>92334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136121</t>
+          <t>132324</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>199560</t>
+          <t>198888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258014</t>
+          <t>259829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>303891</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>374096</t>
+          <t>375812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3140422</t>
+          <t>3144219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3181917</t>
+          <t>3184209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3121183</t>
+          <t>3119368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3179637</t>
+          <t>3180309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6281645</t>
+          <t>6279929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6351850</t>
+          <t>6352118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>41186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51632</t>
+          <t>50988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85982</t>
+          <t>84927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77501</t>
+          <t>77488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114848</t>
+          <t>114326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665154</t>
+          <t>662283</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685211</t>
+          <t>685233</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>611068</t>
+          <t>612123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>645418</t>
+          <t>646062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1285671</t>
+          <t>1286193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1323018</t>
+          <t>1323031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>27206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>50789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76542</t>
+          <t>75762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114765</t>
+          <t>113447</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109465</t>
+          <t>111404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155108</t>
+          <t>157166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>966564</t>
+          <t>967158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>991837</t>
+          <t>990741</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>917419</t>
+          <t>918737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>955642</t>
+          <t>956422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1895023</t>
+          <t>1892965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1940666</t>
+          <t>1938727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>19211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43022</t>
+          <t>41963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56906</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89810</t>
+          <t>89176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83503</t>
+          <t>83758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126730</t>
+          <t>123672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>714601</t>
+          <t>715660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>738652</t>
+          <t>738412</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>687364</t>
+          <t>687998</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>720268</t>
+          <t>719930</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1408067</t>
+          <t>1411125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1451294</t>
+          <t>1451039</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25217</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>51882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>95900</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140464</t>
+          <t>137412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132547</t>
+          <t>131725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181960</t>
+          <t>179867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895962</t>
+          <t>895857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922522</t>
+          <t>922712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>911437</t>
+          <t>914489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>954860</t>
+          <t>956001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1817680</t>
+          <t>1819773</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1867093</t>
+          <t>1867915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>107358</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156398</t>
+          <t>155302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>316576</t>
+          <t>318098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>388206</t>
+          <t>393390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>438667</t>
+          <t>439319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>522074</t>
+          <t>528206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3270381</t>
+          <t>3271477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3319811</t>
+          <t>3319421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3170103</t>
+          <t>3164919</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3241733</t>
+          <t>3240211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6463014</t>
+          <t>6456882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6546421</t>
+          <t>6545769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40670</t>
+          <t>39787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58928</t>
+          <t>58466</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91318</t>
+          <t>91178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85235</t>
+          <t>84184</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124531</t>
+          <t>125813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>634130</t>
+          <t>635013</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>655604</t>
+          <t>655567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>581521</t>
+          <t>581661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>613911</t>
+          <t>614373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1223108</t>
+          <t>1221826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1262404</t>
+          <t>1263455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21685</t>
+          <t>22403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>44581</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74995</t>
+          <t>73627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115818</t>
+          <t>113429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102365</t>
+          <t>103945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149835</t>
+          <t>149867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>979206</t>
+          <t>977850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1000746</t>
+          <t>1000028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>927095</t>
+          <t>929484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>967918</t>
+          <t>969286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1915509</t>
+          <t>1915477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1962979</t>
+          <t>1961399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36431</t>
+          <t>36528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,82 +5328,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>66238</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52065</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>86004</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>91245</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>74153</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>113216</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>51914</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>83534</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>91245</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>73284</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>112933</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>723121</t>
+          <t>723024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>742208</t>
+          <t>742613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,82 +5441,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>718773</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>699007</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>732946</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>91,56%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>89,04%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1453318</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1431347</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1470410</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>92,67%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>95,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>718773</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>701477</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>733097</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>89,36%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>93,39%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1453318</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1431630</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1471279</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>92,69%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>46430</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93884</t>
+          <t>93740</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138405</t>
+          <t>136921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124403</t>
+          <t>124618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175382</t>
+          <t>173035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>888955</t>
+          <t>891137</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>913273</t>
+          <t>913442</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>905374</t>
+          <t>906858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>949895</t>
+          <t>950039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1805964</t>
+          <t>1808311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1856943</t>
+          <t>1856728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99319</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143874</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>312428</t>
+          <t>308721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>390815</t>
+          <t>386225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>422978</t>
+          <t>425038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>509744</t>
+          <t>509279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3250476</t>
+          <t>3252356</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3295031</t>
+          <t>3296544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3153727</t>
+          <t>3158317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3232114</t>
+          <t>3235821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6429148</t>
+          <t>6429613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6515914</t>
+          <t>6513854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65554</t>
+          <t>69391</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52785</t>
+          <t>54880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80637</t>
+          <t>84807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>122230</t>
+          <t>129978</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98488</t>
+          <t>115394</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140201</t>
+          <t>146436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>187784</t>
+          <t>199370</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165495</t>
+          <t>179805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210951</t>
+          <t>221108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>569887</t>
+          <t>621319</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>554804</t>
+          <t>605903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>582656</t>
+          <t>635830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>603100</t>
+          <t>604202</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>585129</t>
+          <t>587744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>626842</t>
+          <t>618786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1172988</t>
+          <t>1225519</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1149821</t>
+          <t>1203781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1195277</t>
+          <t>1245084</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78292</t>
+          <t>85174</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37347</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105847</t>
+          <t>101809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>151707</t>
+          <t>165449</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135388</t>
+          <t>146889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169226</t>
+          <t>183812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>229999</t>
+          <t>250622</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154073</t>
+          <t>225183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>267467</t>
+          <t>276813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1114572</t>
+          <t>963743</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1087017</t>
+          <t>947108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1155517</t>
+          <t>978524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>806944</t>
+          <t>906025</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>789425</t>
+          <t>887662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>823263</t>
+          <t>924585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1921517</t>
+          <t>1869769</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1884049</t>
+          <t>1843578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1997443</t>
+          <t>1895208</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52773</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40740</t>
+          <t>45872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67381</t>
+          <t>75124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>308198</t>
+          <t>119213</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125105</t>
+          <t>101281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>611821</t>
+          <t>135069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>360971</t>
+          <t>178456</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169896</t>
+          <t>156988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>767159</t>
+          <t>203074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>651907</t>
+          <t>743830</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637299</t>
+          <t>727949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663940</t>
+          <t>757201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>625168</t>
+          <t>693046</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321545</t>
+          <t>677190</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>808261</t>
+          <t>710978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1277075</t>
+          <t>1436876</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>870887</t>
+          <t>1412258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1468150</t>
+          <t>1458344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78618</t>
+          <t>82803</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64008</t>
+          <t>67775</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>99148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>186173</t>
+          <t>197766</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151024</t>
+          <t>177945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214421</t>
+          <t>220518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>264791</t>
+          <t>280569</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225749</t>
+          <t>252216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>292210</t>
+          <t>307652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>848213</t>
+          <t>907259</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831943</t>
+          <t>890914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862823</t>
+          <t>922287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>908759</t>
+          <t>921275</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>880511</t>
+          <t>898523</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>943908</t>
+          <t>941096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1756972</t>
+          <t>1828535</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1729553</t>
+          <t>1801452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1796014</t>
+          <t>1856888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>275237</t>
+          <t>296611</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>214747</t>
+          <t>269188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>311928</t>
+          <t>326031</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>768308</t>
+          <t>612406</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>584704</t>
+          <t>577420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1318188</t>
+          <t>648180</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1043545</t>
+          <t>909017</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>840275</t>
+          <t>863262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1625930</t>
+          <t>960896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3184580</t>
+          <t>3236151</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3147889</t>
+          <t>3206731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3245070</t>
+          <t>3263574</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2943972</t>
+          <t>3124548</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2394092</t>
+          <t>3088774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3127576</t>
+          <t>3159534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6128552</t>
+          <t>6360699</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5546167</t>
+          <t>6308820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6331822</t>
+          <t>6406454</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
